--- a/owlcms/src/main/resources/templates/competitionResults/IWF_FlatFile.xlsx
+++ b/owlcms/src/main/resources/templates/competitionResults/IWF_FlatFile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\competitionResults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{71508821-8640-4D8A-ADA4-A736763D9A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB242D8-01C6-49AA-BCBB-84CA9E56271C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="3510" windowWidth="23640" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="CategoryFilter">Results!#REF!</definedName>
     <definedName name="CLUB">Results!#REF!</definedName>
     <definedName name="Collet">#REF!</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">Results!$A$1:$CD$55</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">Results!$A$1:$CD$48</definedName>
     <definedName name="demandé">Results!#REF!</definedName>
     <definedName name="dernier">Results!#REF!</definedName>
     <definedName name="essais">Results!#REF!</definedName>
@@ -56,7 +56,6 @@
     <definedName name="tirage">Results!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -84,7 +83,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">jx:area(lastCell="V2")
 </t>
@@ -245,11 +244,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="167" formatCode="0;\(0\);\-"/>
-    <numFmt numFmtId="169" formatCode="0;\-;\-"/>
-    <numFmt numFmtId="170" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="164" formatCode="0;\(0\);\-"/>
+    <numFmt numFmtId="165" formatCode="0;\-;\-"/>
+    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -317,12 +316,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -494,73 +487,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -1027,161 +1026,161 @@
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="27.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.85546875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="17" style="4" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23" style="4" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="4" customWidth="1"/>
-    <col min="24" max="16384" width="11.42578125" style="4"/>
+    <col min="1" max="1" width="18.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="17" style="3" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23" style="3" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="2" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="R2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="T2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="U2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="21" t="s">
         <v>0</v>
       </c>
     </row>
